--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.46.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.46.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.46.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.46.xlsx
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.46.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.46.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0046.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0046.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -595,18 +595,18 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: being not â€œconsistent with " the above 26th Order. The</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: iff â€˜s bill is,</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]39 *</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]39 *</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L18: isolated marker/symbol line :: 39</t>
@@ -614,13 +614,13 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: %</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]39 *</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: -- â€”69th Order says that Â« The party setting down a 69th new Order</t>
+          <t>L53: punctuation artifact: double/multiple hyphen :: -- —69th Order says that « The party setting down a 69th new Order</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -654,20 +654,16 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: the subpÃ¦na to hear judgment, is not now in force, be-,-</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: -- â€”69th Order says that Â« The party setting down a 69th new Order</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr"/>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L91: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
@@ -701,16 +697,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ nas to hear judgment. The rule does not apply</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: practice :â€”</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr"/>
@@ -734,12 +722,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -748,11 +736,7 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: service of the Subp Ã¦ na to hear judgment. But, although</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
@@ -791,11 +775,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: notice or Subp Ã¦ na in respect of demurrers, and therefore</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
@@ -834,11 +814,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Cause &amp; c., must sue out a Subp Ã¦ na, but it does not</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -877,11 +853,7 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L35: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: subp Ã¦ ena ad</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
@@ -920,11 +892,7 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 69th Order says that â€œThe party setting down a 69th new Order</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
@@ -949,12 +917,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -993,7 +961,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1032,7 +1000,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
